--- a/init_db_scripts/sources/SystemTypes_GIS.xlsx
+++ b/init_db_scripts/sources/SystemTypes_GIS.xlsx
@@ -8,9 +8,9 @@
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="/Users/artemkucher/PycharmProjects/automated-threats-model/init_db_scripts/sources/"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{6DDFB082-3734-0541-BB55-890A109B8A75}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{1BE7A75C-E5A3-B745-A552-1A1479D22014}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
-    <workbookView xWindow="0" yWindow="740" windowWidth="34560" windowHeight="21600" activeTab="1" xr2:uid="{1860FBF2-3CEE-734C-8278-C041533F86CB}"/>
+    <workbookView xWindow="0" yWindow="760" windowWidth="34560" windowHeight="20200" xr2:uid="{1860FBF2-3CEE-734C-8278-C041533F86CB}"/>
   </bookViews>
   <sheets>
     <sheet name="GIS" sheetId="1" r:id="rId1"/>
@@ -605,7 +605,7 @@
   <sheetFormatPr baseColWidth="10" defaultRowHeight="16"/>
   <cols>
     <col min="3" max="3" width="48" customWidth="1"/>
-    <col min="4" max="4" width="16.33203125" customWidth="1"/>
+    <col min="4" max="4" width="16.33203125" style="2" customWidth="1"/>
   </cols>
   <sheetData>
     <row r="1" spans="1:4">
@@ -618,7 +618,7 @@
       <c r="C1" t="s">
         <v>43</v>
       </c>
-      <c r="D1" t="s">
+      <c r="D1" s="2" t="s">
         <v>44</v>
       </c>
     </row>
@@ -646,7 +646,7 @@
       <c r="C3" s="2" t="s">
         <v>0</v>
       </c>
-      <c r="D3" s="1" t="s">
+      <c r="D3" s="3" t="s">
         <v>49</v>
       </c>
     </row>
@@ -688,7 +688,7 @@
       <c r="C6" s="1" t="s">
         <v>1</v>
       </c>
-      <c r="D6" s="1" t="s">
+      <c r="D6" s="3" t="s">
         <v>49</v>
       </c>
     </row>
@@ -730,7 +730,7 @@
       <c r="C9" s="1" t="s">
         <v>3</v>
       </c>
-      <c r="D9" s="1" t="s">
+      <c r="D9" s="3" t="s">
         <v>49</v>
       </c>
     </row>
@@ -772,7 +772,7 @@
       <c r="C12" s="1" t="s">
         <v>2</v>
       </c>
-      <c r="D12" s="1" t="s">
+      <c r="D12" s="3" t="s">
         <v>49</v>
       </c>
     </row>
@@ -814,7 +814,7 @@
       <c r="C15" s="1" t="s">
         <v>51</v>
       </c>
-      <c r="D15" s="1" t="s">
+      <c r="D15" s="3" t="s">
         <v>49</v>
       </c>
     </row>
@@ -856,7 +856,7 @@
       <c r="C18" s="1" t="s">
         <v>4</v>
       </c>
-      <c r="D18" s="1" t="s">
+      <c r="D18" s="3" t="s">
         <v>49</v>
       </c>
     </row>
@@ -898,7 +898,7 @@
       <c r="C21" s="1" t="s">
         <v>5</v>
       </c>
-      <c r="D21" s="1" t="s">
+      <c r="D21" s="3" t="s">
         <v>49</v>
       </c>
     </row>
@@ -940,7 +940,7 @@
       <c r="C24" s="2" t="s">
         <v>0</v>
       </c>
-      <c r="D24" s="1" t="s">
+      <c r="D24" s="3" t="s">
         <v>49</v>
       </c>
     </row>
@@ -982,7 +982,7 @@
       <c r="C27" s="1" t="s">
         <v>1</v>
       </c>
-      <c r="D27" s="1" t="s">
+      <c r="D27" s="3" t="s">
         <v>49</v>
       </c>
     </row>
@@ -1024,7 +1024,7 @@
       <c r="C30" s="1" t="s">
         <v>3</v>
       </c>
-      <c r="D30" s="1" t="s">
+      <c r="D30" s="3" t="s">
         <v>49</v>
       </c>
     </row>
@@ -1066,7 +1066,7 @@
       <c r="C33" s="1" t="s">
         <v>2</v>
       </c>
-      <c r="D33" s="1" t="s">
+      <c r="D33" s="3" t="s">
         <v>49</v>
       </c>
     </row>
@@ -1108,7 +1108,7 @@
       <c r="C36" s="1" t="s">
         <v>51</v>
       </c>
-      <c r="D36" s="1" t="s">
+      <c r="D36" s="3" t="s">
         <v>49</v>
       </c>
     </row>
@@ -1150,7 +1150,7 @@
       <c r="C39" s="1" t="s">
         <v>4</v>
       </c>
-      <c r="D39" s="1" t="s">
+      <c r="D39" s="3" t="s">
         <v>49</v>
       </c>
     </row>
@@ -1192,7 +1192,7 @@
       <c r="C42" s="1" t="s">
         <v>5</v>
       </c>
-      <c r="D42" s="1" t="s">
+      <c r="D42" s="3" t="s">
         <v>49</v>
       </c>
     </row>
@@ -1234,7 +1234,7 @@
       <c r="C45" s="2" t="s">
         <v>0</v>
       </c>
-      <c r="D45" s="1" t="s">
+      <c r="D45" s="3" t="s">
         <v>49</v>
       </c>
     </row>
@@ -1276,7 +1276,7 @@
       <c r="C48" s="1" t="s">
         <v>1</v>
       </c>
-      <c r="D48" s="1" t="s">
+      <c r="D48" s="3" t="s">
         <v>49</v>
       </c>
     </row>
@@ -1318,7 +1318,7 @@
       <c r="C51" s="1" t="s">
         <v>3</v>
       </c>
-      <c r="D51" s="1" t="s">
+      <c r="D51" s="3" t="s">
         <v>49</v>
       </c>
     </row>
@@ -1360,7 +1360,7 @@
       <c r="C54" s="1" t="s">
         <v>2</v>
       </c>
-      <c r="D54" s="1" t="s">
+      <c r="D54" s="3" t="s">
         <v>49</v>
       </c>
     </row>
@@ -1402,7 +1402,7 @@
       <c r="C57" s="1" t="s">
         <v>51</v>
       </c>
-      <c r="D57" s="1" t="s">
+      <c r="D57" s="3" t="s">
         <v>49</v>
       </c>
     </row>
@@ -1444,7 +1444,7 @@
       <c r="C60" s="1" t="s">
         <v>4</v>
       </c>
-      <c r="D60" s="1" t="s">
+      <c r="D60" s="3" t="s">
         <v>49</v>
       </c>
     </row>
@@ -1486,7 +1486,7 @@
       <c r="C63" s="1" t="s">
         <v>5</v>
       </c>
-      <c r="D63" s="1" t="s">
+      <c r="D63" s="3" t="s">
         <v>49</v>
       </c>
     </row>
@@ -1504,398 +1504,334 @@
         <v>50</v>
       </c>
     </row>
-    <row r="65" spans="1:4">
+    <row r="65" spans="1:3">
       <c r="A65" s="2"/>
       <c r="B65" s="1"/>
       <c r="C65" s="3"/>
-      <c r="D65" s="2"/>
-    </row>
-    <row r="66" spans="1:4">
+    </row>
+    <row r="66" spans="1:3">
       <c r="A66" s="2"/>
       <c r="B66" s="1"/>
       <c r="C66" s="2"/>
-      <c r="D66" s="2"/>
-    </row>
-    <row r="67" spans="1:4">
+    </row>
+    <row r="67" spans="1:3">
       <c r="A67" s="2"/>
       <c r="B67" s="1"/>
       <c r="C67" s="2"/>
-      <c r="D67" s="2"/>
-    </row>
-    <row r="68" spans="1:4">
+    </row>
+    <row r="68" spans="1:3">
       <c r="A68" s="2"/>
       <c r="B68" s="1"/>
       <c r="C68" s="2"/>
-      <c r="D68" s="2"/>
-    </row>
-    <row r="69" spans="1:4">
+    </row>
+    <row r="69" spans="1:3">
       <c r="A69" s="2"/>
       <c r="B69" s="1"/>
       <c r="C69" s="2"/>
-      <c r="D69" s="2"/>
-    </row>
-    <row r="70" spans="1:4">
+    </row>
+    <row r="70" spans="1:3">
       <c r="A70" s="2"/>
       <c r="B70" s="1"/>
       <c r="C70" s="2"/>
-      <c r="D70" s="2"/>
-    </row>
-    <row r="71" spans="1:4">
+    </row>
+    <row r="71" spans="1:3">
       <c r="A71" s="2"/>
       <c r="B71" s="1"/>
       <c r="C71" s="2"/>
-      <c r="D71" s="2"/>
-    </row>
-    <row r="72" spans="1:4">
+    </row>
+    <row r="72" spans="1:3">
       <c r="A72" s="2"/>
       <c r="B72" s="1"/>
       <c r="C72" s="2"/>
-      <c r="D72" s="2"/>
-    </row>
-    <row r="73" spans="1:4">
+    </row>
+    <row r="73" spans="1:3">
       <c r="A73" s="2"/>
       <c r="B73" s="1"/>
       <c r="C73" s="2"/>
-      <c r="D73" s="2"/>
-    </row>
-    <row r="74" spans="1:4">
+    </row>
+    <row r="74" spans="1:3">
       <c r="A74" s="2"/>
       <c r="B74" s="1"/>
       <c r="C74" s="2"/>
-      <c r="D74" s="2"/>
-    </row>
-    <row r="75" spans="1:4">
+    </row>
+    <row r="75" spans="1:3">
       <c r="A75" s="2"/>
       <c r="B75" s="1"/>
       <c r="C75" s="2"/>
-      <c r="D75" s="2"/>
-    </row>
-    <row r="76" spans="1:4">
+    </row>
+    <row r="76" spans="1:3">
       <c r="A76" s="2"/>
       <c r="B76" s="1"/>
       <c r="C76" s="2"/>
-      <c r="D76" s="2"/>
-    </row>
-    <row r="77" spans="1:4">
+    </row>
+    <row r="77" spans="1:3">
       <c r="A77" s="2"/>
       <c r="B77" s="1"/>
       <c r="C77" s="2"/>
-      <c r="D77" s="2"/>
-    </row>
-    <row r="78" spans="1:4">
+    </row>
+    <row r="78" spans="1:3">
       <c r="A78" s="2"/>
       <c r="B78" s="1"/>
       <c r="C78" s="2"/>
-      <c r="D78" s="2"/>
-    </row>
-    <row r="79" spans="1:4">
+    </row>
+    <row r="79" spans="1:3">
       <c r="A79" s="2"/>
       <c r="B79" s="1"/>
       <c r="C79" s="2"/>
-      <c r="D79" s="2"/>
-    </row>
-    <row r="80" spans="1:4">
+    </row>
+    <row r="80" spans="1:3">
       <c r="A80" s="2"/>
       <c r="B80" s="1"/>
       <c r="C80" s="2"/>
-      <c r="D80" s="2"/>
-    </row>
-    <row r="81" spans="1:4">
+    </row>
+    <row r="81" spans="1:3">
       <c r="A81" s="2"/>
       <c r="B81" s="1"/>
       <c r="C81" s="2"/>
-      <c r="D81" s="2"/>
-    </row>
-    <row r="82" spans="1:4">
+    </row>
+    <row r="82" spans="1:3">
       <c r="A82" s="2"/>
       <c r="B82" s="1"/>
       <c r="C82" s="3"/>
-      <c r="D82" s="2"/>
-    </row>
-    <row r="83" spans="1:4">
+    </row>
+    <row r="83" spans="1:3">
       <c r="A83" s="2"/>
       <c r="B83" s="1"/>
       <c r="C83" s="3"/>
-      <c r="D83" s="2"/>
-    </row>
-    <row r="84" spans="1:4">
+    </row>
+    <row r="84" spans="1:3">
       <c r="A84" s="2"/>
       <c r="B84" s="1"/>
       <c r="C84" s="3"/>
-      <c r="D84" s="2"/>
-    </row>
-    <row r="85" spans="1:4">
+    </row>
+    <row r="85" spans="1:3">
       <c r="A85" s="2"/>
       <c r="B85" s="1"/>
       <c r="C85" s="3"/>
-      <c r="D85" s="2"/>
-    </row>
-    <row r="86" spans="1:4">
+    </row>
+    <row r="86" spans="1:3">
       <c r="A86" s="2"/>
       <c r="B86" s="1"/>
       <c r="C86" s="3"/>
-      <c r="D86" s="2"/>
-    </row>
-    <row r="87" spans="1:4">
+    </row>
+    <row r="87" spans="1:3">
       <c r="A87" s="2"/>
       <c r="B87" s="1"/>
       <c r="C87" s="3"/>
-      <c r="D87" s="2"/>
-    </row>
-    <row r="88" spans="1:4">
+    </row>
+    <row r="88" spans="1:3">
       <c r="A88" s="2"/>
       <c r="B88" s="1"/>
       <c r="C88" s="3"/>
-      <c r="D88" s="2"/>
-    </row>
-    <row r="89" spans="1:4">
+    </row>
+    <row r="89" spans="1:3">
       <c r="A89" s="2"/>
       <c r="B89" s="1"/>
       <c r="C89" s="3"/>
-      <c r="D89" s="2"/>
-    </row>
-    <row r="90" spans="1:4">
+    </row>
+    <row r="90" spans="1:3">
       <c r="A90" s="2"/>
       <c r="B90" s="1"/>
       <c r="C90" s="3"/>
-      <c r="D90" s="2"/>
-    </row>
-    <row r="91" spans="1:4">
+    </row>
+    <row r="91" spans="1:3">
       <c r="A91" s="2"/>
       <c r="B91" s="1"/>
       <c r="C91" s="3"/>
-      <c r="D91" s="2"/>
-    </row>
-    <row r="92" spans="1:4">
+    </row>
+    <row r="92" spans="1:3">
       <c r="A92" s="2"/>
       <c r="B92" s="1"/>
       <c r="C92" s="3"/>
-      <c r="D92" s="2"/>
-    </row>
-    <row r="93" spans="1:4">
+    </row>
+    <row r="93" spans="1:3">
       <c r="A93" s="2"/>
       <c r="B93" s="1"/>
       <c r="C93" s="3"/>
-      <c r="D93" s="2"/>
-    </row>
-    <row r="94" spans="1:4">
+    </row>
+    <row r="94" spans="1:3">
       <c r="A94" s="2"/>
       <c r="B94" s="1"/>
       <c r="C94" s="3"/>
-      <c r="D94" s="2"/>
-    </row>
-    <row r="95" spans="1:4">
+    </row>
+    <row r="95" spans="1:3">
       <c r="A95" s="2"/>
       <c r="B95" s="1"/>
       <c r="C95" s="3"/>
-      <c r="D95" s="2"/>
-    </row>
-    <row r="96" spans="1:4">
+    </row>
+    <row r="96" spans="1:3">
       <c r="A96" s="2"/>
       <c r="B96" s="1"/>
       <c r="C96" s="3"/>
-      <c r="D96" s="2"/>
-    </row>
-    <row r="97" spans="1:4">
+    </row>
+    <row r="97" spans="1:3">
       <c r="A97" s="2"/>
       <c r="B97" s="1"/>
       <c r="C97" s="3"/>
-      <c r="D97" s="2"/>
-    </row>
-    <row r="98" spans="1:4">
+    </row>
+    <row r="98" spans="1:3">
       <c r="A98" s="2"/>
       <c r="B98" s="1"/>
       <c r="C98" s="2"/>
-      <c r="D98" s="2"/>
-    </row>
-    <row r="99" spans="1:4">
+    </row>
+    <row r="99" spans="1:3">
       <c r="A99" s="2"/>
       <c r="B99" s="1"/>
       <c r="C99" s="2"/>
-      <c r="D99" s="2"/>
-    </row>
-    <row r="100" spans="1:4">
+    </row>
+    <row r="100" spans="1:3">
       <c r="A100" s="2"/>
       <c r="B100" s="1"/>
       <c r="C100" s="2"/>
-      <c r="D100" s="2"/>
-    </row>
-    <row r="101" spans="1:4">
+    </row>
+    <row r="101" spans="1:3">
       <c r="A101" s="2"/>
       <c r="B101" s="1"/>
       <c r="C101" s="2"/>
-      <c r="D101" s="2"/>
-    </row>
-    <row r="102" spans="1:4">
+    </row>
+    <row r="102" spans="1:3">
       <c r="A102" s="2"/>
       <c r="B102" s="1"/>
       <c r="C102" s="2"/>
-      <c r="D102" s="2"/>
-    </row>
-    <row r="103" spans="1:4">
+    </row>
+    <row r="103" spans="1:3">
       <c r="A103" s="2"/>
       <c r="B103" s="1"/>
       <c r="C103" s="2"/>
-      <c r="D103" s="2"/>
-    </row>
-    <row r="104" spans="1:4">
+    </row>
+    <row r="104" spans="1:3">
       <c r="A104" s="2"/>
       <c r="B104" s="1"/>
       <c r="C104" s="2"/>
-      <c r="D104" s="2"/>
-    </row>
-    <row r="105" spans="1:4">
+    </row>
+    <row r="105" spans="1:3">
       <c r="A105" s="2"/>
       <c r="B105" s="1"/>
       <c r="C105" s="2"/>
-      <c r="D105" s="2"/>
-    </row>
-    <row r="106" spans="1:4">
+    </row>
+    <row r="106" spans="1:3">
       <c r="A106" s="2"/>
       <c r="B106" s="1"/>
       <c r="C106" s="2"/>
-      <c r="D106" s="2"/>
-    </row>
-    <row r="107" spans="1:4">
+    </row>
+    <row r="107" spans="1:3">
       <c r="A107" s="2"/>
       <c r="B107" s="1"/>
       <c r="C107" s="2"/>
-      <c r="D107" s="2"/>
-    </row>
-    <row r="108" spans="1:4">
+    </row>
+    <row r="108" spans="1:3">
       <c r="A108" s="2"/>
       <c r="B108" s="1"/>
       <c r="C108" s="2"/>
-      <c r="D108" s="2"/>
-    </row>
-    <row r="109" spans="1:4">
+    </row>
+    <row r="109" spans="1:3">
       <c r="A109" s="2"/>
       <c r="B109" s="1"/>
       <c r="C109" s="2"/>
-      <c r="D109" s="2"/>
-    </row>
-    <row r="110" spans="1:4">
+    </row>
+    <row r="110" spans="1:3">
       <c r="A110" s="2"/>
       <c r="B110" s="1"/>
       <c r="C110" s="2"/>
-      <c r="D110" s="2"/>
-    </row>
-    <row r="111" spans="1:4">
+    </row>
+    <row r="111" spans="1:3">
       <c r="A111" s="2"/>
       <c r="B111" s="1"/>
       <c r="C111" s="2"/>
-      <c r="D111" s="2"/>
-    </row>
-    <row r="112" spans="1:4">
+    </row>
+    <row r="112" spans="1:3">
       <c r="A112" s="2"/>
       <c r="B112" s="1"/>
       <c r="C112" s="2"/>
-      <c r="D112" s="2"/>
-    </row>
-    <row r="113" spans="1:4">
+    </row>
+    <row r="113" spans="1:3">
       <c r="A113" s="2"/>
       <c r="B113" s="1"/>
       <c r="C113" s="2"/>
-      <c r="D113" s="2"/>
-    </row>
-    <row r="114" spans="1:4">
+    </row>
+    <row r="114" spans="1:3">
       <c r="A114" s="2"/>
       <c r="B114" s="1"/>
       <c r="C114" s="3"/>
-      <c r="D114" s="2"/>
-    </row>
-    <row r="115" spans="1:4">
+    </row>
+    <row r="115" spans="1:3">
       <c r="A115" s="2"/>
       <c r="B115" s="1"/>
       <c r="C115" s="3"/>
-      <c r="D115" s="2"/>
-    </row>
-    <row r="116" spans="1:4">
+    </row>
+    <row r="116" spans="1:3">
       <c r="A116" s="2"/>
       <c r="B116" s="1"/>
       <c r="C116" s="3"/>
-      <c r="D116" s="2"/>
-    </row>
-    <row r="117" spans="1:4">
+    </row>
+    <row r="117" spans="1:3">
       <c r="A117" s="2"/>
       <c r="B117" s="1"/>
       <c r="C117" s="3"/>
-      <c r="D117" s="2"/>
-    </row>
-    <row r="118" spans="1:4">
+    </row>
+    <row r="118" spans="1:3">
       <c r="A118" s="2"/>
       <c r="B118" s="1"/>
       <c r="C118" s="3"/>
-      <c r="D118" s="2"/>
-    </row>
-    <row r="119" spans="1:4">
+    </row>
+    <row r="119" spans="1:3">
       <c r="A119" s="2"/>
       <c r="B119" s="1"/>
       <c r="C119" s="3"/>
-      <c r="D119" s="2"/>
-    </row>
-    <row r="120" spans="1:4">
+    </row>
+    <row r="120" spans="1:3">
       <c r="A120" s="2"/>
       <c r="B120" s="1"/>
       <c r="C120" s="3"/>
-      <c r="D120" s="2"/>
-    </row>
-    <row r="121" spans="1:4">
+    </row>
+    <row r="121" spans="1:3">
       <c r="A121" s="2"/>
       <c r="B121" s="1"/>
       <c r="C121" s="3"/>
-      <c r="D121" s="2"/>
-    </row>
-    <row r="122" spans="1:4">
+    </row>
+    <row r="122" spans="1:3">
       <c r="A122" s="2"/>
       <c r="B122" s="1"/>
       <c r="C122" s="3"/>
-      <c r="D122" s="2"/>
-    </row>
-    <row r="123" spans="1:4">
+    </row>
+    <row r="123" spans="1:3">
       <c r="A123" s="2"/>
       <c r="B123" s="1"/>
       <c r="C123" s="3"/>
-      <c r="D123" s="2"/>
-    </row>
-    <row r="124" spans="1:4">
+    </row>
+    <row r="124" spans="1:3">
       <c r="A124" s="2"/>
       <c r="B124" s="1"/>
       <c r="C124" s="3"/>
-      <c r="D124" s="2"/>
-    </row>
-    <row r="125" spans="1:4">
+    </row>
+    <row r="125" spans="1:3">
       <c r="A125" s="2"/>
       <c r="B125" s="1"/>
       <c r="C125" s="3"/>
-      <c r="D125" s="2"/>
-    </row>
-    <row r="126" spans="1:4">
+    </row>
+    <row r="126" spans="1:3">
       <c r="A126" s="2"/>
       <c r="B126" s="1"/>
       <c r="C126" s="3"/>
-      <c r="D126" s="2"/>
-    </row>
-    <row r="127" spans="1:4">
+    </row>
+    <row r="127" spans="1:3">
       <c r="A127" s="2"/>
       <c r="B127" s="1"/>
       <c r="C127" s="3"/>
-      <c r="D127" s="2"/>
-    </row>
-    <row r="128" spans="1:4">
+    </row>
+    <row r="128" spans="1:3">
       <c r="A128" s="2"/>
       <c r="B128" s="1"/>
       <c r="C128" s="3"/>
-      <c r="D128" s="2"/>
-    </row>
-    <row r="129" spans="1:4">
+    </row>
+    <row r="129" spans="1:3">
       <c r="A129" s="2"/>
       <c r="B129" s="1"/>
       <c r="C129" s="3"/>
-      <c r="D129" s="2"/>
     </row>
   </sheetData>
   <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
+  <pageSetup paperSize="9" orientation="portrait" horizontalDpi="0" verticalDpi="0"/>
 </worksheet>
 </file>
 
@@ -6993,7 +6929,7 @@
     </row>
     <row r="244" spans="1:10">
       <c r="A244" s="2" t="str">
-        <f t="shared" ref="A244:B307" si="0">_xlfn.CONCAT("INSERT INTO app_ispdnclass_negative_consequences  (ispdnclass_id, negativeconsequence_id) VALUES (", A3, ",", B3, ");")</f>
+        <f t="shared" ref="A244:A307" si="0">_xlfn.CONCAT("INSERT INTO app_ispdnclass_negative_consequences  (ispdnclass_id, negativeconsequence_id) VALUES (", A3, ",", B3, ");")</f>
         <v>INSERT INTO app_ispdnclass_negative_consequences  (ispdnclass_id, negativeconsequence_id) VALUES (43,12);</v>
       </c>
       <c r="D244" s="2"/>
@@ -7997,7 +7933,7 @@
     </row>
     <row r="308" spans="1:9">
       <c r="A308" s="2" t="str">
-        <f t="shared" ref="A308:B371" si="66">_xlfn.CONCAT("INSERT INTO app_ispdnclass_negative_consequences  (ispdnclass_id, negativeconsequence_id) VALUES (", A67, ",", B67, ");")</f>
+        <f t="shared" ref="A308:A371" si="66">_xlfn.CONCAT("INSERT INTO app_ispdnclass_negative_consequences  (ispdnclass_id, negativeconsequence_id) VALUES (", A67, ",", B67, ");")</f>
         <v>INSERT INTO app_ispdnclass_negative_consequences  (ispdnclass_id, negativeconsequence_id) VALUES (46,44);</v>
       </c>
       <c r="E308" s="2" t="str">
@@ -8893,7 +8829,7 @@
     </row>
     <row r="372" spans="1:9">
       <c r="A372" s="2" t="str">
-        <f t="shared" ref="A372:B435" si="132">_xlfn.CONCAT("INSERT INTO app_ispdnclass_negative_consequences  (ispdnclass_id, negativeconsequence_id) VALUES (", A131, ",", B131, ");")</f>
+        <f t="shared" ref="A372:A435" si="132">_xlfn.CONCAT("INSERT INTO app_ispdnclass_negative_consequences  (ispdnclass_id, negativeconsequence_id) VALUES (", A131, ",", B131, ");")</f>
         <v>INSERT INTO app_ispdnclass_negative_consequences  (ispdnclass_id, negativeconsequence_id) VALUES (52,63);</v>
       </c>
       <c r="E372" s="2" t="str">
@@ -9789,7 +9725,7 @@
     </row>
     <row r="436" spans="1:9">
       <c r="A436" s="2" t="str">
-        <f t="shared" ref="A436:B443" si="198">_xlfn.CONCAT("INSERT INTO app_ispdnclass_negative_consequences  (ispdnclass_id, negativeconsequence_id) VALUES (", A195, ",", B195, ");")</f>
+        <f t="shared" ref="A436:A443" si="198">_xlfn.CONCAT("INSERT INTO app_ispdnclass_negative_consequences  (ispdnclass_id, negativeconsequence_id) VALUES (", A195, ",", B195, ");")</f>
         <v>INSERT INTO app_ispdnclass_negative_consequences  (ispdnclass_id, negativeconsequence_id) VALUES (58,58);</v>
       </c>
       <c r="E436" s="2" t="str">
@@ -9915,7 +9851,7 @@
     </row>
     <row r="445" spans="1:9">
       <c r="A445" s="2" t="str">
-        <f t="shared" ref="A445:B508" si="208">_xlfn.CONCAT("INSERT INTO app_ispdnclass_negative_consequences  (ispdnclass_id, negativeconsequence_id) VALUES (", A204, ",", B204, ");")</f>
+        <f t="shared" ref="A445:A482" si="208">_xlfn.CONCAT("INSERT INTO app_ispdnclass_negative_consequences  (ispdnclass_id, negativeconsequence_id) VALUES (", A204, ",", B204, ");")</f>
         <v>INSERT INTO app_ispdnclass_negative_consequences  (ispdnclass_id, negativeconsequence_id) VALUES (58,50);</v>
       </c>
       <c r="E445" s="2" t="str">
@@ -19456,7 +19392,7 @@
     </row>
     <row r="491" spans="1:9">
       <c r="A491" s="2" t="str">
-        <f t="shared" ref="A491:A523" si="15">_xlfn.CONCAT("INSERT INTO app_ispdnclass_negative_consequences  (ispdnclass_id, negativeconsequence_id) VALUES (", A236, ",", B236, ");")</f>
+        <f t="shared" ref="A491:A510" si="15">_xlfn.CONCAT("INSERT INTO app_ispdnclass_negative_consequences  (ispdnclass_id, negativeconsequence_id) VALUES (", A236, ",", B236, ");")</f>
         <v>INSERT INTO app_ispdnclass_negative_consequences  (ispdnclass_id, negativeconsequence_id) VALUES (40,35);</v>
       </c>
       <c r="E491" s="2" t="str">
@@ -27552,7 +27488,7 @@
     </row>
     <row r="435" spans="1:9">
       <c r="A435" t="str">
-        <f t="shared" ref="A435:A498" si="9">_xlfn.CONCAT("INSERT INTO app_ispdnclass_negative_consequences  (ispdnclass_id, negativeconsequence_id) VALUES (", A195, ",", B195, ");")</f>
+        <f t="shared" ref="A435:A480" si="9">_xlfn.CONCAT("INSERT INTO app_ispdnclass_negative_consequences  (ispdnclass_id, negativeconsequence_id) VALUES (", A195, ",", B195, ");")</f>
         <v>INSERT INTO app_ispdnclass_negative_consequences  (ispdnclass_id, negativeconsequence_id) VALUES (16,58);</v>
       </c>
       <c r="E435" t="str">
@@ -28208,7 +28144,7 @@
     <col min="2" max="2" width="74" customWidth="1"/>
   </cols>
   <sheetData>
-    <row r="1" spans="1:4">
+    <row r="1" spans="1:4" ht="34">
       <c r="A1">
         <v>7</v>
       </c>
@@ -28222,7 +28158,7 @@
         <v>7</v>
       </c>
     </row>
-    <row r="2" spans="1:4">
+    <row r="2" spans="1:4" ht="17">
       <c r="A2">
         <v>12</v>
       </c>
@@ -28236,7 +28172,7 @@
         <v>1</v>
       </c>
     </row>
-    <row r="3" spans="1:4">
+    <row r="3" spans="1:4" ht="17">
       <c r="A3">
         <v>13</v>
       </c>
@@ -28250,7 +28186,7 @@
         <v>2</v>
       </c>
     </row>
-    <row r="4" spans="1:4">
+    <row r="4" spans="1:4" ht="17">
       <c r="A4">
         <v>14</v>
       </c>
@@ -28264,7 +28200,7 @@
         <v>3</v>
       </c>
     </row>
-    <row r="5" spans="1:4">
+    <row r="5" spans="1:4" ht="17">
       <c r="A5">
         <v>15</v>
       </c>
@@ -28278,7 +28214,7 @@
         <v>4</v>
       </c>
     </row>
-    <row r="6" spans="1:4">
+    <row r="6" spans="1:4" ht="17">
       <c r="A6">
         <v>16</v>
       </c>
@@ -28292,7 +28228,7 @@
         <v>5</v>
       </c>
     </row>
-    <row r="7" spans="1:4">
+    <row r="7" spans="1:4" ht="17">
       <c r="A7">
         <v>18</v>
       </c>
@@ -28306,7 +28242,7 @@
         <v>7</v>
       </c>
     </row>
-    <row r="8" spans="1:4">
+    <row r="8" spans="1:4" ht="17">
       <c r="A8">
         <v>19</v>
       </c>
@@ -28320,7 +28256,7 @@
         <v>8</v>
       </c>
     </row>
-    <row r="9" spans="1:4">
+    <row r="9" spans="1:4" ht="17">
       <c r="A9">
         <v>22</v>
       </c>
@@ -28334,7 +28270,7 @@
         <v>11</v>
       </c>
     </row>
-    <row r="10" spans="1:4">
+    <row r="10" spans="1:4" ht="17">
       <c r="A10">
         <v>24</v>
       </c>
@@ -28348,7 +28284,7 @@
         <v>13</v>
       </c>
     </row>
-    <row r="11" spans="1:4">
+    <row r="11" spans="1:4" ht="17">
       <c r="A11">
         <v>25</v>
       </c>
@@ -28362,7 +28298,7 @@
         <v>14</v>
       </c>
     </row>
-    <row r="12" spans="1:4">
+    <row r="12" spans="1:4" ht="17">
       <c r="A12">
         <v>26</v>
       </c>
@@ -28376,7 +28312,7 @@
         <v>15</v>
       </c>
     </row>
-    <row r="13" spans="1:4">
+    <row r="13" spans="1:4" ht="17">
       <c r="A13">
         <v>27</v>
       </c>
@@ -28390,7 +28326,7 @@
         <v>16</v>
       </c>
     </row>
-    <row r="14" spans="1:4">
+    <row r="14" spans="1:4" ht="17">
       <c r="A14">
         <v>28</v>
       </c>
@@ -28404,7 +28340,7 @@
         <v>17</v>
       </c>
     </row>
-    <row r="15" spans="1:4">
+    <row r="15" spans="1:4" ht="17">
       <c r="A15">
         <v>29</v>
       </c>
@@ -28418,7 +28354,7 @@
         <v>18</v>
       </c>
     </row>
-    <row r="16" spans="1:4">
+    <row r="16" spans="1:4" ht="34">
       <c r="A16">
         <v>30</v>
       </c>
@@ -28432,7 +28368,7 @@
         <v>19</v>
       </c>
     </row>
-    <row r="17" spans="1:4">
+    <row r="17" spans="1:4" ht="17">
       <c r="A17">
         <v>31</v>
       </c>
@@ -28446,7 +28382,7 @@
         <v>20</v>
       </c>
     </row>
-    <row r="18" spans="1:4">
+    <row r="18" spans="1:4" ht="17">
       <c r="A18">
         <v>32</v>
       </c>
@@ -28460,7 +28396,7 @@
         <v>21</v>
       </c>
     </row>
-    <row r="19" spans="1:4">
+    <row r="19" spans="1:4" ht="17">
       <c r="A19">
         <v>33</v>
       </c>
@@ -28474,7 +28410,7 @@
         <v>22</v>
       </c>
     </row>
-    <row r="20" spans="1:4">
+    <row r="20" spans="1:4" ht="34">
       <c r="A20">
         <v>34</v>
       </c>
@@ -28488,7 +28424,7 @@
         <v>23</v>
       </c>
     </row>
-    <row r="21" spans="1:4">
+    <row r="21" spans="1:4" ht="34">
       <c r="A21">
         <v>35</v>
       </c>
@@ -28502,7 +28438,7 @@
         <v>24</v>
       </c>
     </row>
-    <row r="22" spans="1:4">
+    <row r="22" spans="1:4" ht="34">
       <c r="A22">
         <v>36</v>
       </c>
@@ -28516,7 +28452,7 @@
         <v>25</v>
       </c>
     </row>
-    <row r="23" spans="1:4">
+    <row r="23" spans="1:4" ht="17">
       <c r="A23">
         <v>37</v>
       </c>
@@ -28530,7 +28466,7 @@
         <v>1</v>
       </c>
     </row>
-    <row r="24" spans="1:4">
+    <row r="24" spans="1:4" ht="34">
       <c r="A24">
         <v>38</v>
       </c>
@@ -28544,7 +28480,7 @@
         <v>2</v>
       </c>
     </row>
-    <row r="25" spans="1:4">
+    <row r="25" spans="1:4" ht="34">
       <c r="A25">
         <v>40</v>
       </c>
@@ -28558,7 +28494,7 @@
         <v>4</v>
       </c>
     </row>
-    <row r="26" spans="1:4">
+    <row r="26" spans="1:4" ht="17">
       <c r="A26">
         <v>41</v>
       </c>
@@ -28572,7 +28508,7 @@
         <v>5</v>
       </c>
     </row>
-    <row r="27" spans="1:4">
+    <row r="27" spans="1:4" ht="17">
       <c r="A27">
         <v>42</v>
       </c>
@@ -28586,7 +28522,7 @@
         <v>6</v>
       </c>
     </row>
-    <row r="28" spans="1:4">
+    <row r="28" spans="1:4" ht="51">
       <c r="A28">
         <v>43</v>
       </c>
@@ -28600,7 +28536,7 @@
         <v>7</v>
       </c>
     </row>
-    <row r="29" spans="1:4">
+    <row r="29" spans="1:4" ht="34">
       <c r="A29">
         <v>44</v>
       </c>
@@ -28614,7 +28550,7 @@
         <v>8</v>
       </c>
     </row>
-    <row r="30" spans="1:4">
+    <row r="30" spans="1:4" ht="17">
       <c r="A30">
         <v>45</v>
       </c>
@@ -28628,7 +28564,7 @@
         <v>9</v>
       </c>
     </row>
-    <row r="31" spans="1:4">
+    <row r="31" spans="1:4" ht="34">
       <c r="A31">
         <v>48</v>
       </c>
@@ -28642,7 +28578,7 @@
         <v>12</v>
       </c>
     </row>
-    <row r="32" spans="1:4">
+    <row r="32" spans="1:4" ht="17">
       <c r="A32">
         <v>49</v>
       </c>
@@ -28656,7 +28592,7 @@
         <v>13</v>
       </c>
     </row>
-    <row r="33" spans="1:4">
+    <row r="33" spans="1:4" ht="34">
       <c r="A33">
         <v>50</v>
       </c>
